--- a/modulo5/planilla/Leads_NexoDigital.xlsx
+++ b/modulo5/planilla/Leads_NexoDigital.xlsx
@@ -647,7 +647,7 @@
       <formula1>"Sí,No"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✅ Correcto,✅ No sé correcto,⚠️ Falla de recuperación,❌ Alucinación"</formula1>
+      <formula1>"✅ Correcto,✅ Correcto (aplicó la regla No sé),⚠️ Falla de recuperación,❌ Alucinación"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
